--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y347"/>
+  <dimension ref="A1:Y350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28463,6 +28463,249 @@
         <v>363.4</v>
       </c>
       <c r="Y347" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>335.77</v>
+      </c>
+      <c r="C348" t="n">
+        <v>308.47</v>
+      </c>
+      <c r="D348" t="n">
+        <v>290.18</v>
+      </c>
+      <c r="E348" t="n">
+        <v>300.8</v>
+      </c>
+      <c r="F348" t="n">
+        <v>308.49</v>
+      </c>
+      <c r="G348" t="n">
+        <v>330.42</v>
+      </c>
+      <c r="H348" t="n">
+        <v>313.74</v>
+      </c>
+      <c r="I348" t="n">
+        <v>312.84</v>
+      </c>
+      <c r="J348" t="n">
+        <v>305.77</v>
+      </c>
+      <c r="K348" t="n">
+        <v>288.91</v>
+      </c>
+      <c r="L348" t="n">
+        <v>310.87</v>
+      </c>
+      <c r="M348" t="n">
+        <v>304.87</v>
+      </c>
+      <c r="N348" t="n">
+        <v>296.12</v>
+      </c>
+      <c r="O348" t="n">
+        <v>311.78</v>
+      </c>
+      <c r="P348" t="n">
+        <v>344.9</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>353.42</v>
+      </c>
+      <c r="R348" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="S348" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="T348" t="n">
+        <v>345.66</v>
+      </c>
+      <c r="U348" t="n">
+        <v>345.63</v>
+      </c>
+      <c r="V348" t="n">
+        <v>341.86</v>
+      </c>
+      <c r="W348" t="n">
+        <v>355.45</v>
+      </c>
+      <c r="X348" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>334.97</v>
+      </c>
+      <c r="C349" t="n">
+        <v>308.52</v>
+      </c>
+      <c r="D349" t="n">
+        <v>283.63</v>
+      </c>
+      <c r="E349" t="n">
+        <v>303.18</v>
+      </c>
+      <c r="F349" t="n">
+        <v>304.63</v>
+      </c>
+      <c r="G349" t="n">
+        <v>330.15</v>
+      </c>
+      <c r="H349" t="n">
+        <v>310.36</v>
+      </c>
+      <c r="I349" t="n">
+        <v>312.84</v>
+      </c>
+      <c r="J349" t="n">
+        <v>305.77</v>
+      </c>
+      <c r="K349" t="n">
+        <v>279.18</v>
+      </c>
+      <c r="L349" t="n">
+        <v>301.68</v>
+      </c>
+      <c r="M349" t="n">
+        <v>292.4</v>
+      </c>
+      <c r="N349" t="n">
+        <v>287.53</v>
+      </c>
+      <c r="O349" t="n">
+        <v>300.87</v>
+      </c>
+      <c r="P349" t="n">
+        <v>342.66</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="R349" t="n">
+        <v>352.44</v>
+      </c>
+      <c r="S349" t="n">
+        <v>346.32</v>
+      </c>
+      <c r="T349" t="n">
+        <v>346.24</v>
+      </c>
+      <c r="U349" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="V349" t="n">
+        <v>343.37</v>
+      </c>
+      <c r="W349" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="X349" t="n">
+        <v>366.21</v>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>334.05</v>
+      </c>
+      <c r="C350" t="n">
+        <v>307.59</v>
+      </c>
+      <c r="D350" t="n">
+        <v>281.87</v>
+      </c>
+      <c r="E350" t="n">
+        <v>300.89</v>
+      </c>
+      <c r="F350" t="n">
+        <v>303.54</v>
+      </c>
+      <c r="G350" t="n">
+        <v>329.61</v>
+      </c>
+      <c r="H350" t="n">
+        <v>310.36</v>
+      </c>
+      <c r="I350" t="n">
+        <v>312.84</v>
+      </c>
+      <c r="J350" t="n">
+        <v>305.77</v>
+      </c>
+      <c r="K350" t="n">
+        <v>268.24</v>
+      </c>
+      <c r="L350" t="n">
+        <v>298.71</v>
+      </c>
+      <c r="M350" t="n">
+        <v>290.37</v>
+      </c>
+      <c r="N350" t="n">
+        <v>286.69</v>
+      </c>
+      <c r="O350" t="n">
+        <v>299.21</v>
+      </c>
+      <c r="P350" t="n">
+        <v>345.84</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>354.42</v>
+      </c>
+      <c r="R350" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="S350" t="n">
+        <v>347.63</v>
+      </c>
+      <c r="T350" t="n">
+        <v>346.46</v>
+      </c>
+      <c r="U350" t="n">
+        <v>344.52</v>
+      </c>
+      <c r="V350" t="n">
+        <v>342.71</v>
+      </c>
+      <c r="W350" t="n">
+        <v>357.02</v>
+      </c>
+      <c r="X350" t="n">
+        <v>366.98</v>
+      </c>
+      <c r="Y350" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28479,7 +28722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32032,6 +32275,36 @@
       </c>
       <c r="B355" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
@@ -32200,28 +32473,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3380009138883273</v>
+        <v>-0.3108604397896966</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1449537762692654</v>
+        <v>0.1204027415631834</v>
       </c>
       <c r="M2" t="n">
-        <v>4.638996379619591</v>
+        <v>4.766236532293465</v>
       </c>
       <c r="N2" t="n">
-        <v>37.2187223951915</v>
+        <v>39.31026383412588</v>
       </c>
       <c r="O2" t="n">
-        <v>6.100714908532565</v>
+        <v>6.26978977591162</v>
       </c>
       <c r="P2" t="n">
-        <v>327.0038024941933</v>
+        <v>326.709526021415</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32278,28 +32551,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4061475069697784</v>
+        <v>-0.3771617760624557</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1209497608996013</v>
+        <v>0.1038001798994368</v>
       </c>
       <c r="M3" t="n">
-        <v>6.318747008350343</v>
+        <v>6.433760687725553</v>
       </c>
       <c r="N3" t="n">
-        <v>66.21279461866338</v>
+        <v>68.38953389331182</v>
       </c>
       <c r="O3" t="n">
-        <v>8.137124468672171</v>
+        <v>8.269796484394995</v>
       </c>
       <c r="P3" t="n">
-        <v>300.9242293663224</v>
+        <v>300.609939456733</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32356,28 +32629,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1055695234315465</v>
+        <v>-0.08980569868583904</v>
       </c>
       <c r="J4" t="n">
+        <v>349</v>
+      </c>
+      <c r="K4" t="n">
         <v>346</v>
       </c>
-      <c r="K4" t="n">
-        <v>343</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.005070136522824398</v>
+        <v>0.00370815372727118</v>
       </c>
       <c r="M4" t="n">
-        <v>8.586855871116562</v>
+        <v>8.596064301598116</v>
       </c>
       <c r="N4" t="n">
-        <v>119.8902656143511</v>
+        <v>119.7671266380595</v>
       </c>
       <c r="O4" t="n">
-        <v>10.94944133800218</v>
+        <v>10.94381682220877</v>
       </c>
       <c r="P4" t="n">
-        <v>278.2659320888848</v>
+        <v>278.0941063769831</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32434,28 +32707,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1302125797326745</v>
+        <v>-0.1079898745419251</v>
       </c>
       <c r="J5" t="n">
+        <v>349</v>
+      </c>
+      <c r="K5" t="n">
         <v>346</v>
       </c>
-      <c r="K5" t="n">
-        <v>343</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.008274043074382953</v>
+        <v>0.00571982132689508</v>
       </c>
       <c r="M5" t="n">
-        <v>7.813286258641899</v>
+        <v>7.861385978015629</v>
       </c>
       <c r="N5" t="n">
-        <v>111.1249434420667</v>
+        <v>111.7645827186204</v>
       </c>
       <c r="O5" t="n">
-        <v>10.54158163854299</v>
+        <v>10.5718769723555</v>
       </c>
       <c r="P5" t="n">
-        <v>291.3532421357866</v>
+        <v>291.1106021399904</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32512,28 +32785,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2496094318312437</v>
+        <v>-0.2569122343005311</v>
       </c>
       <c r="J6" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0172866012187598</v>
+        <v>0.01857958284707095</v>
       </c>
       <c r="M6" t="n">
-        <v>11.57621501340498</v>
+        <v>11.51224755256527</v>
       </c>
       <c r="N6" t="n">
-        <v>195.0899644958681</v>
+        <v>193.6015336278892</v>
       </c>
       <c r="O6" t="n">
-        <v>13.96746091800038</v>
+        <v>13.91407681550915</v>
       </c>
       <c r="P6" t="n">
-        <v>316.709921696128</v>
+        <v>316.7894647096615</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32590,28 +32863,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0848296335137633</v>
+        <v>0.07847940814458794</v>
       </c>
       <c r="J7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K7" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003259496942368378</v>
+        <v>0.002835492853139221</v>
       </c>
       <c r="M7" t="n">
-        <v>8.735054763663756</v>
+        <v>8.693177742272898</v>
       </c>
       <c r="N7" t="n">
-        <v>121.3071555767591</v>
+        <v>120.3965844645652</v>
       </c>
       <c r="O7" t="n">
-        <v>11.0139527680465</v>
+        <v>10.97253774040287</v>
       </c>
       <c r="P7" t="n">
-        <v>331.7644930230948</v>
+        <v>331.8333047774104</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32668,28 +32941,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3190529906710373</v>
+        <v>0.282449525710025</v>
       </c>
       <c r="J8" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K8" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03416635158490966</v>
+        <v>0.02669879740712933</v>
       </c>
       <c r="M8" t="n">
-        <v>9.865590031486841</v>
+        <v>9.960895759682431</v>
       </c>
       <c r="N8" t="n">
-        <v>158.7364123290663</v>
+        <v>161.7588952248273</v>
       </c>
       <c r="O8" t="n">
-        <v>12.59906394654247</v>
+        <v>12.71844704454232</v>
       </c>
       <c r="P8" t="n">
-        <v>325.8097067593864</v>
+        <v>326.2065531539137</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32746,28 +33019,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2077676164997153</v>
+        <v>0.183944101607768</v>
       </c>
       <c r="J9" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K9" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0134548174177278</v>
+        <v>0.01064480306191218</v>
       </c>
       <c r="M9" t="n">
-        <v>10.47236326852221</v>
+        <v>10.51811770256868</v>
       </c>
       <c r="N9" t="n">
-        <v>170.9899792668685</v>
+        <v>171.3030994642845</v>
       </c>
       <c r="O9" t="n">
-        <v>13.07631367270105</v>
+        <v>13.08828099730001</v>
       </c>
       <c r="P9" t="n">
-        <v>321.8899973061266</v>
+        <v>322.1522575661918</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32824,28 +33097,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.015969749239461</v>
+        <v>-1.014940194768972</v>
       </c>
       <c r="J10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K10" t="n">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05178936214124086</v>
+        <v>0.05253022040682698</v>
       </c>
       <c r="M10" t="n">
-        <v>21.2241322239454</v>
+        <v>21.04052467075885</v>
       </c>
       <c r="N10" t="n">
-        <v>1041.783808102817</v>
+        <v>1032.675431753013</v>
       </c>
       <c r="O10" t="n">
-        <v>32.27667591470375</v>
+        <v>32.13526772493132</v>
       </c>
       <c r="P10" t="n">
-        <v>332.125298148104</v>
+        <v>332.1141092814977</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32902,28 +33175,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8420331512791492</v>
+        <v>-0.8976572571075665</v>
       </c>
       <c r="J11" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K11" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02963944926224493</v>
+        <v>0.03383671948853439</v>
       </c>
       <c r="M11" t="n">
-        <v>26.31556543207968</v>
+        <v>26.47600953451734</v>
       </c>
       <c r="N11" t="n">
-        <v>1264.446709161219</v>
+        <v>1263.738203509359</v>
       </c>
       <c r="O11" t="n">
-        <v>35.55905945270796</v>
+        <v>35.54909567779973</v>
       </c>
       <c r="P11" t="n">
-        <v>334.9497640440117</v>
+        <v>335.5597837857525</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32980,28 +33253,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06616242615271747</v>
+        <v>-0.1035273149556147</v>
       </c>
       <c r="J12" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K12" t="n">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003796139556014877</v>
+        <v>0.0009379249816929836</v>
       </c>
       <c r="M12" t="n">
-        <v>20.2513617656634</v>
+        <v>20.28431863738978</v>
       </c>
       <c r="N12" t="n">
-        <v>633.18322172534</v>
+        <v>632.3890283750121</v>
       </c>
       <c r="O12" t="n">
-        <v>25.16313219226375</v>
+        <v>25.1473463485715</v>
       </c>
       <c r="P12" t="n">
-        <v>328.5028119480291</v>
+        <v>328.9089143519741</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33058,28 +33331,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6982975226559193</v>
+        <v>0.6354041561387977</v>
       </c>
       <c r="J13" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K13" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0416752058991533</v>
+        <v>0.03462402308854085</v>
       </c>
       <c r="M13" t="n">
-        <v>20.17759251018267</v>
+        <v>20.3745879459244</v>
       </c>
       <c r="N13" t="n">
-        <v>610.4397290293646</v>
+        <v>618.0118251482427</v>
       </c>
       <c r="O13" t="n">
-        <v>24.7070785207269</v>
+        <v>24.8598436267858</v>
       </c>
       <c r="P13" t="n">
-        <v>315.7341582247729</v>
+        <v>316.4220010193485</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33136,28 +33409,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04117816761434455</v>
+        <v>-0.0214040313310609</v>
       </c>
       <c r="J14" t="n">
+        <v>349</v>
+      </c>
+      <c r="K14" t="n">
         <v>346</v>
       </c>
-      <c r="K14" t="n">
-        <v>343</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.0001662926617617133</v>
+        <v>4.466687670257041e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>19.73529613653014</v>
+        <v>19.92227013655495</v>
       </c>
       <c r="N14" t="n">
-        <v>558.6000740888064</v>
+        <v>566.5865950456048</v>
       </c>
       <c r="O14" t="n">
-        <v>23.63472178995992</v>
+        <v>23.80307952861572</v>
       </c>
       <c r="P14" t="n">
-        <v>327.7431157362971</v>
+        <v>328.4257538579129</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33214,28 +33487,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2860493062086067</v>
+        <v>-0.3351085651994423</v>
       </c>
       <c r="J15" t="n">
+        <v>349</v>
+      </c>
+      <c r="K15" t="n">
         <v>346</v>
       </c>
-      <c r="K15" t="n">
-        <v>343</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.00804007276319052</v>
+        <v>0.01102696892744881</v>
       </c>
       <c r="M15" t="n">
-        <v>19.44305793611063</v>
+        <v>19.56406081735299</v>
       </c>
       <c r="N15" t="n">
-        <v>553.1312714722401</v>
+        <v>556.3902085678211</v>
       </c>
       <c r="O15" t="n">
-        <v>23.51874298240108</v>
+        <v>23.58792505855106</v>
       </c>
       <c r="P15" t="n">
-        <v>341.9042935177076</v>
+        <v>342.4394570031288</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33292,28 +33565,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1000273036029642</v>
+        <v>0.08702259512440753</v>
       </c>
       <c r="J16" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K16" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003670003349405815</v>
+        <v>0.002817145452565839</v>
       </c>
       <c r="M16" t="n">
-        <v>9.787316969024587</v>
+        <v>9.782897086703752</v>
       </c>
       <c r="N16" t="n">
-        <v>149.9190954196091</v>
+        <v>149.1906848381852</v>
       </c>
       <c r="O16" t="n">
-        <v>12.24414535276387</v>
+        <v>12.2143638736606</v>
       </c>
       <c r="P16" t="n">
-        <v>349.8882432987892</v>
+        <v>350.0289594100175</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33370,28 +33643,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1867263761425021</v>
+        <v>0.1856812516461621</v>
       </c>
       <c r="J17" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K17" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01666037171175894</v>
+        <v>0.01675284918240472</v>
       </c>
       <c r="M17" t="n">
-        <v>7.651504390941679</v>
+        <v>7.592161866936292</v>
       </c>
       <c r="N17" t="n">
-        <v>113.5213081339235</v>
+        <v>112.5488443950626</v>
       </c>
       <c r="O17" t="n">
-        <v>10.65463786967551</v>
+        <v>10.60890401479166</v>
       </c>
       <c r="P17" t="n">
-        <v>349.3519160970074</v>
+        <v>349.3632404383746</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33448,28 +33721,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2655971259154432</v>
+        <v>0.2664026112947745</v>
       </c>
       <c r="J18" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K18" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03900143830321556</v>
+        <v>0.03987026470290334</v>
       </c>
       <c r="M18" t="n">
-        <v>7.708870917073014</v>
+        <v>7.646786935713018</v>
       </c>
       <c r="N18" t="n">
-        <v>95.81832311947691</v>
+        <v>94.99969903179313</v>
       </c>
       <c r="O18" t="n">
-        <v>9.788683421148981</v>
+        <v>9.746778905453489</v>
       </c>
       <c r="P18" t="n">
-        <v>345.4463611379949</v>
+        <v>345.4376271474973</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33526,28 +33799,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2682332024457916</v>
+        <v>0.2657009497389441</v>
       </c>
       <c r="J19" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K19" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03301967734248201</v>
+        <v>0.03294206772545705</v>
       </c>
       <c r="M19" t="n">
-        <v>8.673320106823478</v>
+        <v>8.611652494269917</v>
       </c>
       <c r="N19" t="n">
-        <v>116.4496139228876</v>
+        <v>115.4830599787681</v>
       </c>
       <c r="O19" t="n">
-        <v>10.79118223008432</v>
+        <v>10.7463044800884</v>
       </c>
       <c r="P19" t="n">
-        <v>340.4414624288825</v>
+        <v>340.4688837238836</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33604,28 +33877,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5146693228932174</v>
+        <v>0.5123289432337123</v>
       </c>
       <c r="J20" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K20" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09354874497006471</v>
+        <v>0.09420238728159103</v>
       </c>
       <c r="M20" t="n">
-        <v>9.408492991457413</v>
+        <v>9.338999390073356</v>
       </c>
       <c r="N20" t="n">
-        <v>141.4890283279201</v>
+        <v>140.291551769675</v>
       </c>
       <c r="O20" t="n">
-        <v>11.89491607065473</v>
+        <v>11.84447346949939</v>
       </c>
       <c r="P20" t="n">
-        <v>333.9046940056733</v>
+        <v>333.9300481426117</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33682,28 +33955,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5521300125668938</v>
+        <v>0.5510054097662612</v>
       </c>
       <c r="J21" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K21" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09823836566301936</v>
+        <v>0.09937569751850428</v>
       </c>
       <c r="M21" t="n">
-        <v>10.06694230815042</v>
+        <v>9.986388446649663</v>
       </c>
       <c r="N21" t="n">
-        <v>154.7404325351309</v>
+        <v>153.4086079913667</v>
       </c>
       <c r="O21" t="n">
-        <v>12.43947074980005</v>
+        <v>12.3858228629093</v>
       </c>
       <c r="P21" t="n">
-        <v>331.1471075854585</v>
+        <v>331.1592966875803</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33760,28 +34033,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5544413976137492</v>
+        <v>0.552729194562422</v>
       </c>
       <c r="J22" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K22" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09494192525308154</v>
+        <v>0.09586050468524276</v>
       </c>
       <c r="M22" t="n">
-        <v>10.16852786571663</v>
+        <v>10.09103597948653</v>
       </c>
       <c r="N22" t="n">
-        <v>161.6504459784663</v>
+        <v>160.2697097644605</v>
       </c>
       <c r="O22" t="n">
-        <v>12.71418286711601</v>
+        <v>12.65976736612725</v>
       </c>
       <c r="P22" t="n">
-        <v>328.9822460781666</v>
+        <v>329.0008034005322</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33838,28 +34111,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4890768807185916</v>
+        <v>0.5129069611599176</v>
       </c>
       <c r="J23" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K23" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07570727014055589</v>
+        <v>0.08304711109845631</v>
       </c>
       <c r="M23" t="n">
-        <v>10.00817393423064</v>
+        <v>10.04160902781471</v>
       </c>
       <c r="N23" t="n">
-        <v>161.0917919058778</v>
+        <v>161.558790306313</v>
       </c>
       <c r="O23" t="n">
-        <v>12.69219413284708</v>
+        <v>12.71057789033657</v>
       </c>
       <c r="P23" t="n">
-        <v>328.5552191128295</v>
+        <v>328.2968628457504</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33916,28 +34189,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6245362048303668</v>
+        <v>0.6625736613217581</v>
       </c>
       <c r="J24" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K24" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1124750365858672</v>
+        <v>0.1236564299037065</v>
       </c>
       <c r="M24" t="n">
-        <v>10.35872995900633</v>
+        <v>10.48333383524816</v>
       </c>
       <c r="N24" t="n">
-        <v>169.6677823412375</v>
+        <v>172.9380308711172</v>
       </c>
       <c r="O24" t="n">
-        <v>13.02565861449</v>
+        <v>13.15059051416009</v>
       </c>
       <c r="P24" t="n">
-        <v>325.2257131563309</v>
+        <v>324.8135426036329</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33975,7 +34248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y347"/>
+  <dimension ref="A1:Y350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77815,6 +78088,387 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-38.49562489346812,174.6356906566736</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-38.49505083118781,174.6363015003539</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-38.494449074590136,174.6368152385849</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-38.49375847469072,174.63701741217895</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-38.493050306247724,174.63726294887417</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-38.49227910588565,174.63723451465393</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>-38.491547584583245,174.63742813844505</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>-38.490844374890195,174.63743846787574</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-38.49014050862112,174.63751952346647</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-38.489435604403305,174.6377127985922</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-38.48873478152688,174.63746108717612</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-38.48802351851452,174.63752979732462</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-38.48730118423645,174.6376003813137</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-38.48660138851872,174.63736216835423</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-38.48592262295495,174.6369250850179</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-38.48522683909425,174.6367691656683</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>-38.48452470060495,174.63671816669995</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>-38.4838169682412,174.63675951326428</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>-38.483116406511485,174.63668222685098</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>-38.482414683195465,174.63662402672682</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>-38.481710367008745,174.63660856951927</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>-38.48101804750953,174.63639471306635</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>-38.48032180739347,174.63624554415918</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-38.49562735183593,174.63569927841678</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-38.49505067754206,174.63630096149834</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-38.494469201925824,174.6368858281955</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-38.49375116125178,174.6369917630727</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-38.493060018628256,174.63730544002175</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-38.492279353116864,174.6372375939253</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>-38.49154722865903,174.6374668839479</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>-38.490844374890195,174.63743846787574</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-38.49014050862112,174.63751952346647</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-38.489434579556544,174.63782433192983</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-38.48873381380471,174.63756642957657</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-38.48802039949131,174.63767269070624</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-38.487296516706664,174.63769867161648</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-38.48659384386628,174.6374868625657</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-38.48592107402128,174.63695068653755</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>-38.48522664548208,174.63677236582814</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>-38.48452447933546,174.63672182399014</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>-38.483818558621664,174.63673322674856</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>-38.48311680756019,174.63667559814118</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>-38.48241438586844,174.6366289410677</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>-38.481711411106794,174.63659131235002</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>-38.481018918717716,174.63638031317865</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>-38.480323764111326,174.63621320185945</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-38.49563017895811,174.63570919342212</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-38.49505353535264,174.63631098421257</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-38.4944746101796,174.636904795792</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-38.49375819813221,174.63701644225466</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>-38.49306276124064,174.6373174388193</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-38.49227984757904,174.6372437524681</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>-38.49154722865903,174.6374668839479</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-38.490844374890195,174.63743846787574</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-38.49014050862112,174.63751952346647</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-38.48943342713544,174.63794973528366</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-38.48873350103856,174.63760047385483</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-38.488019891726864,174.63769595241777</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-38.487296060273266,174.63770828324013</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-38.48659269590575,174.63750583528446</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-38.485923272952256,174.63691434152267</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>-38.485227530565595,174.63675773652596</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>-38.48452542664467,174.63670616621624</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>-38.48381946444443,174.6367182548629</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>-38.48311695968199,174.63667308380298</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>-38.48241391567645,174.63663671258342</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>-38.48171095474636,174.63659885521878</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>-38.48101913306232,174.63637677034907</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>-38.480324296502985,174.63620440201075</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0260/nzd0260.xlsx
+++ b/data/nzd0260/nzd0260.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y350"/>
+  <dimension ref="A1:Y351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28661,7 +28661,7 @@
         <v>312.84</v>
       </c>
       <c r="J350" t="n">
-        <v>305.77</v>
+        <v>281.84</v>
       </c>
       <c r="K350" t="n">
         <v>268.24</v>
@@ -28708,6 +28708,87 @@
       <c r="Y350" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>333.93</v>
+      </c>
+      <c r="C351" t="n">
+        <v>307.59</v>
+      </c>
+      <c r="D351" t="n">
+        <v>282.87</v>
+      </c>
+      <c r="E351" t="n">
+        <v>302.91</v>
+      </c>
+      <c r="F351" t="n">
+        <v>304.51</v>
+      </c>
+      <c r="G351" t="n">
+        <v>329.04</v>
+      </c>
+      <c r="H351" t="n">
+        <v>309.86</v>
+      </c>
+      <c r="I351" t="n">
+        <v>312.84</v>
+      </c>
+      <c r="J351" t="n">
+        <v>260.42</v>
+      </c>
+      <c r="K351" t="n">
+        <v>268.24</v>
+      </c>
+      <c r="L351" t="n">
+        <v>298.71</v>
+      </c>
+      <c r="M351" t="n">
+        <v>286.08</v>
+      </c>
+      <c r="N351" t="n">
+        <v>285.06</v>
+      </c>
+      <c r="O351" t="n">
+        <v>295.94</v>
+      </c>
+      <c r="P351" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="R351" t="n">
+        <v>353.35</v>
+      </c>
+      <c r="S351" t="n">
+        <v>349.36</v>
+      </c>
+      <c r="T351" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="U351" t="n">
+        <v>343.54</v>
+      </c>
+      <c r="V351" t="n">
+        <v>344.24</v>
+      </c>
+      <c r="W351" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="X351" t="n">
+        <v>367.15</v>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28722,7 +28803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32305,6 +32386,16 @@
       </c>
       <c r="B358" t="n">
         <v>1.01</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -32473,28 +32564,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3108604397896966</v>
+        <v>-0.3026047223000726</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1204027415631834</v>
+        <v>0.113628098794312</v>
       </c>
       <c r="M2" t="n">
-        <v>4.766236532293465</v>
+        <v>4.80508916388085</v>
       </c>
       <c r="N2" t="n">
-        <v>39.31026383412588</v>
+        <v>39.88127170983524</v>
       </c>
       <c r="O2" t="n">
-        <v>6.26978977591162</v>
+        <v>6.315162049372545</v>
       </c>
       <c r="P2" t="n">
-        <v>326.709526021415</v>
+        <v>326.6198208774816</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32551,28 +32642,28 @@
         <v>0.1297</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3771617760624557</v>
+        <v>-0.3680953082914574</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1038001798994368</v>
+        <v>0.0987816164168378</v>
       </c>
       <c r="M3" t="n">
-        <v>6.433760687725553</v>
+        <v>6.467976578550473</v>
       </c>
       <c r="N3" t="n">
-        <v>68.38953389331182</v>
+        <v>69.01791477885551</v>
       </c>
       <c r="O3" t="n">
-        <v>8.269796484394995</v>
+        <v>8.307702135901089</v>
       </c>
       <c r="P3" t="n">
-        <v>300.609939456733</v>
+        <v>300.5114248458119</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32629,28 +32720,28 @@
         <v>0.1644</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08980569868583904</v>
+        <v>-0.085964519138886</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00370815372727118</v>
+        <v>0.003413490030525157</v>
       </c>
       <c r="M4" t="n">
-        <v>8.596064301598116</v>
+        <v>8.591905962312932</v>
       </c>
       <c r="N4" t="n">
-        <v>119.7671266380595</v>
+        <v>119.5686286331302</v>
       </c>
       <c r="O4" t="n">
-        <v>10.94381682220877</v>
+        <v>10.93474410460209</v>
       </c>
       <c r="P4" t="n">
-        <v>278.0941063769831</v>
+        <v>278.0521377440012</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32707,28 +32798,28 @@
         <v>0.1682</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1079898745419251</v>
+        <v>-0.100107847571673</v>
       </c>
       <c r="J5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00571982132689508</v>
+        <v>0.004919618903524992</v>
       </c>
       <c r="M5" t="n">
-        <v>7.861385978015629</v>
+        <v>7.881109779474757</v>
       </c>
       <c r="N5" t="n">
-        <v>111.7645827186204</v>
+        <v>112.0573677285087</v>
       </c>
       <c r="O5" t="n">
-        <v>10.5718769723555</v>
+        <v>10.58571526768544</v>
       </c>
       <c r="P5" t="n">
-        <v>291.1106021399904</v>
+        <v>291.0243630466431</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32785,28 +32876,28 @@
         <v>0.1057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2569122343005311</v>
+        <v>-0.259827531658246</v>
       </c>
       <c r="J6" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01857958284707095</v>
+        <v>0.01909092472254958</v>
       </c>
       <c r="M6" t="n">
-        <v>11.51224755256527</v>
+        <v>11.49376892700459</v>
       </c>
       <c r="N6" t="n">
-        <v>193.6015336278892</v>
+        <v>193.1254749096406</v>
       </c>
       <c r="O6" t="n">
-        <v>13.91407681550915</v>
+        <v>13.89695919651636</v>
       </c>
       <c r="P6" t="n">
-        <v>316.7894647096615</v>
+        <v>316.8212731248811</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32863,28 +32954,28 @@
         <v>0.1291</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07847940814458794</v>
+        <v>0.07587845014440196</v>
       </c>
       <c r="J7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002835492853139221</v>
+        <v>0.002664407691421289</v>
       </c>
       <c r="M7" t="n">
-        <v>8.693177742272898</v>
+        <v>8.68184995319082</v>
       </c>
       <c r="N7" t="n">
-        <v>120.3965844645652</v>
+        <v>120.1201693805354</v>
       </c>
       <c r="O7" t="n">
-        <v>10.97253774040287</v>
+        <v>10.95993473431915</v>
       </c>
       <c r="P7" t="n">
-        <v>331.8333047774104</v>
+        <v>331.8615456398317</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32941,28 +33032,28 @@
         <v>0.1133</v>
       </c>
       <c r="I8" t="n">
-        <v>0.282449525710025</v>
+        <v>0.2697372774902456</v>
       </c>
       <c r="J8" t="n">
+        <v>350</v>
+      </c>
+      <c r="K8" t="n">
         <v>349</v>
       </c>
-      <c r="K8" t="n">
-        <v>348</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.02669879740712933</v>
+        <v>0.02430188449888915</v>
       </c>
       <c r="M8" t="n">
-        <v>9.960895759682431</v>
+        <v>9.99479025383248</v>
       </c>
       <c r="N8" t="n">
-        <v>161.7588952248273</v>
+        <v>162.9128550653026</v>
       </c>
       <c r="O8" t="n">
-        <v>12.71844704454232</v>
+        <v>12.76373201948798</v>
       </c>
       <c r="P8" t="n">
-        <v>326.2065531539137</v>
+        <v>326.3446568451557</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33019,28 +33110,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.183944101607768</v>
+        <v>0.1762331426997098</v>
       </c>
       <c r="J9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K9" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01064480306191218</v>
+        <v>0.009801043812501575</v>
       </c>
       <c r="M9" t="n">
-        <v>10.51811770256868</v>
+        <v>10.53181087865513</v>
       </c>
       <c r="N9" t="n">
-        <v>171.3030994642845</v>
+        <v>171.3867766305174</v>
       </c>
       <c r="O9" t="n">
-        <v>13.08828099730001</v>
+        <v>13.09147725165183</v>
       </c>
       <c r="P9" t="n">
-        <v>322.1522575661918</v>
+        <v>322.237318071687</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33097,28 +33188,28 @@
         <v>0.08790000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.014940194768972</v>
+        <v>-1.051858043646115</v>
       </c>
       <c r="J10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K10" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05253022040682698</v>
+        <v>0.05612623664194183</v>
       </c>
       <c r="M10" t="n">
-        <v>21.04052467075885</v>
+        <v>21.29607922883512</v>
       </c>
       <c r="N10" t="n">
-        <v>1032.675431753013</v>
+        <v>1036.937652036616</v>
       </c>
       <c r="O10" t="n">
-        <v>32.13526772493132</v>
+        <v>32.20151630027096</v>
       </c>
       <c r="P10" t="n">
-        <v>332.1141092814977</v>
+        <v>332.5160052825119</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33175,28 +33266,28 @@
         <v>0.0462</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8976572571075665</v>
+        <v>-0.9213668358843135</v>
       </c>
       <c r="J11" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K11" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03383671948853439</v>
+        <v>0.03562754365139031</v>
       </c>
       <c r="M11" t="n">
-        <v>26.47600953451734</v>
+        <v>26.56561838770407</v>
       </c>
       <c r="N11" t="n">
-        <v>1263.738203509359</v>
+        <v>1265.515591349103</v>
       </c>
       <c r="O11" t="n">
-        <v>35.54909567779973</v>
+        <v>35.57408595240506</v>
       </c>
       <c r="P11" t="n">
-        <v>335.5597837857525</v>
+        <v>335.8202889875918</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33253,28 +33344,28 @@
         <v>0.0351</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1035273149556147</v>
+        <v>-0.1183258991860197</v>
       </c>
       <c r="J12" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K12" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0009379249816929836</v>
+        <v>0.001227576726278934</v>
       </c>
       <c r="M12" t="n">
-        <v>20.28431863738978</v>
+        <v>20.30938435394934</v>
       </c>
       <c r="N12" t="n">
-        <v>632.3890283750121</v>
+        <v>632.7196371556619</v>
       </c>
       <c r="O12" t="n">
-        <v>25.1473463485715</v>
+        <v>25.15391892241966</v>
       </c>
       <c r="P12" t="n">
-        <v>328.9089143519741</v>
+        <v>329.0700579061707</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33331,28 +33422,28 @@
         <v>0.098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6354041561387977</v>
+        <v>0.6097317662050524</v>
       </c>
       <c r="J13" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K13" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03462402308854085</v>
+        <v>0.03182462111192785</v>
       </c>
       <c r="M13" t="n">
-        <v>20.3745879459244</v>
+        <v>20.4709041398293</v>
       </c>
       <c r="N13" t="n">
-        <v>618.0118251482427</v>
+        <v>622.6364564731905</v>
       </c>
       <c r="O13" t="n">
-        <v>24.8598436267858</v>
+        <v>24.95268435405679</v>
       </c>
       <c r="P13" t="n">
-        <v>316.4220010193485</v>
+        <v>316.7033132140743</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33409,28 +33500,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0214040313310609</v>
+        <v>-0.04435723159163619</v>
       </c>
       <c r="J14" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K14" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L14" t="n">
-        <v>4.466687670257041e-05</v>
+        <v>0.000191104238245754</v>
       </c>
       <c r="M14" t="n">
-        <v>19.92227013655495</v>
+        <v>19.99845583063717</v>
       </c>
       <c r="N14" t="n">
-        <v>566.5865950456048</v>
+        <v>570.1870683709228</v>
       </c>
       <c r="O14" t="n">
-        <v>23.80307952861572</v>
+        <v>23.8785901671544</v>
       </c>
       <c r="P14" t="n">
-        <v>328.4257538579129</v>
+        <v>328.6766248056003</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33487,28 +33578,28 @@
         <v>0.0863</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3351085651994423</v>
+        <v>-0.3552682861442948</v>
       </c>
       <c r="J15" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K15" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01102696892744881</v>
+        <v>0.01235606645491105</v>
       </c>
       <c r="M15" t="n">
-        <v>19.56406081735299</v>
+        <v>19.62834641763524</v>
       </c>
       <c r="N15" t="n">
-        <v>556.3902085678211</v>
+        <v>558.8237637347722</v>
       </c>
       <c r="O15" t="n">
-        <v>23.58792505855106</v>
+        <v>23.63945354137384</v>
       </c>
       <c r="P15" t="n">
-        <v>342.4394570031288</v>
+        <v>342.6597961384621</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33565,28 +33656,28 @@
         <v>0.0584</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08702259512440753</v>
+        <v>0.08449787934609414</v>
       </c>
       <c r="J16" t="n">
+        <v>350</v>
+      </c>
+      <c r="K16" t="n">
         <v>349</v>
       </c>
-      <c r="K16" t="n">
-        <v>348</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.002817145452565839</v>
+        <v>0.002670197823886333</v>
       </c>
       <c r="M16" t="n">
-        <v>9.782897086703752</v>
+        <v>9.770454138277385</v>
       </c>
       <c r="N16" t="n">
-        <v>149.1906848381852</v>
+        <v>148.8266601306761</v>
       </c>
       <c r="O16" t="n">
-        <v>12.2143638736606</v>
+        <v>12.19945327179362</v>
       </c>
       <c r="P16" t="n">
-        <v>350.0289594100175</v>
+        <v>350.0563357047708</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33643,28 +33734,28 @@
         <v>0.061</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1856812516461621</v>
+        <v>0.1858668934844565</v>
       </c>
       <c r="J17" t="n">
+        <v>350</v>
+      </c>
+      <c r="K17" t="n">
         <v>349</v>
       </c>
-      <c r="K17" t="n">
-        <v>348</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01675284918240472</v>
+        <v>0.01687770284144285</v>
       </c>
       <c r="M17" t="n">
-        <v>7.592161866936292</v>
+        <v>7.571330243370099</v>
       </c>
       <c r="N17" t="n">
-        <v>112.5488443950626</v>
+        <v>112.2266998055528</v>
       </c>
       <c r="O17" t="n">
-        <v>10.60890401479166</v>
+        <v>10.59371038897859</v>
       </c>
       <c r="P17" t="n">
-        <v>349.3632404383746</v>
+        <v>349.3612236571827</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33721,28 +33812,28 @@
         <v>0.0711</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2664026112947745</v>
+        <v>0.2668408576615952</v>
       </c>
       <c r="J18" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K18" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03987026470290334</v>
+        <v>0.04020971466746992</v>
       </c>
       <c r="M18" t="n">
-        <v>7.646786935713018</v>
+        <v>7.626997636629124</v>
       </c>
       <c r="N18" t="n">
-        <v>94.99969903179313</v>
+        <v>94.73018979921028</v>
       </c>
       <c r="O18" t="n">
-        <v>9.746778905453489</v>
+        <v>9.732943532108376</v>
       </c>
       <c r="P18" t="n">
-        <v>345.4376271474973</v>
+        <v>345.4328687256577</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33799,28 +33890,28 @@
         <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2657009497389441</v>
+        <v>0.2666701275541036</v>
       </c>
       <c r="J19" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K19" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03294206772545705</v>
+        <v>0.03335062458954441</v>
       </c>
       <c r="M19" t="n">
-        <v>8.611652494269917</v>
+        <v>8.592341127689178</v>
       </c>
       <c r="N19" t="n">
-        <v>115.4830599787681</v>
+        <v>115.1606443812669</v>
       </c>
       <c r="O19" t="n">
-        <v>10.7463044800884</v>
+        <v>10.73129276374785</v>
       </c>
       <c r="P19" t="n">
-        <v>340.4688837238836</v>
+        <v>340.4583582451997</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33877,28 +33968,28 @@
         <v>0.0791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5123289432337123</v>
+        <v>0.5114160661941368</v>
       </c>
       <c r="J20" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K20" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09420238728159103</v>
+        <v>0.0943678805400473</v>
       </c>
       <c r="M20" t="n">
-        <v>9.338999390073356</v>
+        <v>9.316721717796447</v>
       </c>
       <c r="N20" t="n">
-        <v>140.291551769675</v>
+        <v>139.8990430115473</v>
       </c>
       <c r="O20" t="n">
-        <v>11.84447346949939</v>
+        <v>11.827892585391</v>
       </c>
       <c r="P20" t="n">
-        <v>333.9300481426117</v>
+        <v>333.9399600423349</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33955,28 +34046,28 @@
         <v>0.1044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5510054097662612</v>
+        <v>0.5497891511804888</v>
       </c>
       <c r="J21" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K21" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09937569751850428</v>
+        <v>0.09946820028939041</v>
       </c>
       <c r="M21" t="n">
-        <v>9.986388446649663</v>
+        <v>9.964659614938506</v>
       </c>
       <c r="N21" t="n">
-        <v>153.4086079913667</v>
+        <v>152.982638079101</v>
       </c>
       <c r="O21" t="n">
-        <v>12.3858228629093</v>
+        <v>12.3686150428858</v>
       </c>
       <c r="P21" t="n">
-        <v>331.1592966875803</v>
+        <v>331.1724993984757</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -34033,28 +34124,28 @@
         <v>0.1153</v>
       </c>
       <c r="I22" t="n">
-        <v>0.552729194562422</v>
+        <v>0.5530115877369913</v>
       </c>
       <c r="J22" t="n">
+        <v>350</v>
+      </c>
+      <c r="K22" t="n">
         <v>349</v>
       </c>
-      <c r="K22" t="n">
-        <v>348</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.09586050468524276</v>
+        <v>0.09643171829436947</v>
       </c>
       <c r="M22" t="n">
-        <v>10.09103597948653</v>
+        <v>10.06346905302391</v>
       </c>
       <c r="N22" t="n">
-        <v>160.2697097644605</v>
+        <v>159.811282404617</v>
       </c>
       <c r="O22" t="n">
-        <v>12.65976736612725</v>
+        <v>12.64164872176952</v>
       </c>
       <c r="P22" t="n">
-        <v>329.0008034005322</v>
+        <v>328.9977355293645</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34111,28 +34202,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5129069611599176</v>
+        <v>0.5204230128571564</v>
       </c>
       <c r="J23" t="n">
+        <v>350</v>
+      </c>
+      <c r="K23" t="n">
         <v>349</v>
       </c>
-      <c r="K23" t="n">
-        <v>348</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.08304711109845631</v>
+        <v>0.08545004458217087</v>
       </c>
       <c r="M23" t="n">
-        <v>10.04160902781471</v>
+        <v>10.05105068797462</v>
       </c>
       <c r="N23" t="n">
-        <v>161.558790306313</v>
+        <v>161.661284789268</v>
       </c>
       <c r="O23" t="n">
-        <v>12.71057789033657</v>
+        <v>12.71460910878773</v>
       </c>
       <c r="P23" t="n">
-        <v>328.2968628457504</v>
+        <v>328.2152097451336</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34189,28 +34280,28 @@
         <v>0.0646</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6625736613217581</v>
+        <v>0.6757329755355883</v>
       </c>
       <c r="J24" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K24" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1236564299037065</v>
+        <v>0.1274900940478194</v>
       </c>
       <c r="M24" t="n">
-        <v>10.48333383524816</v>
+        <v>10.52711877028031</v>
       </c>
       <c r="N24" t="n">
-        <v>172.9380308711172</v>
+        <v>174.1736863959085</v>
       </c>
       <c r="O24" t="n">
-        <v>13.15059051416009</v>
+        <v>13.19748788201408</v>
       </c>
       <c r="P24" t="n">
-        <v>324.8135426036329</v>
+        <v>324.6706604877957</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34248,7 +34339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y350"/>
+  <dimension ref="A1:Y351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78390,7 +78481,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>-38.49014050862112,174.63751952346647</t>
+          <t>-38.49013798832398,174.6377938316762</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -78466,6 +78557,133 @@
       <c r="Y350" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-38.49563054771313,174.63571048668373</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-38.49505353535264,174.63631098421257</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-38.49447153730853,174.6368940187482</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-38.49375199092791,174.636994672845</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>-38.49306032056728,174.63730676099027</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>-38.492280369511,174.63725025315222</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-38.49154717600642,174.63747261553107</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-38.490844374890195,174.63743846787574</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-38.49013573183417,174.63803936786493</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-38.48943342713544,174.63794973528366</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-38.48873350103856,174.63760047385483</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-38.48801881865283,174.63774511140255</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-38.48729517457288,174.63772693436653</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-38.486590434552824,174.63754320925247</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-38.485924503795516,174.63689399745658</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-38.48522768960385,174.63675510782318</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>-38.48452510857029,174.63671142357106</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>-38.48382066068074,174.63669848283004</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>-38.48311653788955,174.6366800553771</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>-38.4824132380459,174.6366479127088</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>-38.48171201267208,174.63658136947737</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>-38.481018462370784,174.63638785597703</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>-38.480324414043906,174.636202459187</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
